--- a/kaikei_format.xlsx
+++ b/kaikei_format.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/akinobumori/Developer/chonaikai-kaikei/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F84DA0B-7235-FA4E-88EE-7768B54F516B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A64D658-2FE0-6140-B7B3-40FF43EFF4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3520" yWindow="11440" windowWidth="25600" windowHeight="16000" activeTab="1" xr2:uid="{EA7B7210-5B43-9F42-9B31-6CE62E01F660}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="25600" windowHeight="16000" activeTab="3" xr2:uid="{EA7B7210-5B43-9F42-9B31-6CE62E01F660}"/>
   </bookViews>
   <sheets>
     <sheet name="収支（前期）" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="99">
   <si>
     <t>月</t>
   </si>
@@ -829,6 +829,51 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>自治会積立金</t>
+    <rPh sb="0" eb="6">
+      <t>ジチカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前期合計</t>
+    <rPh sb="0" eb="1">
+      <t>ゼn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後期合計</t>
+    <rPh sb="0" eb="4">
+      <t>コウキゴウク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総合計</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ソウ </t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ネンドグ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次年度繰越金</t>
+    <rPh sb="0" eb="6">
+      <t>ジネンド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次年へ繰越金</t>
+    <rPh sb="0" eb="2">
+      <t>ジネn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>前年度繰越金</t>
     <rPh sb="0" eb="6">
       <t>ゼンネンド</t>
@@ -836,40 +881,15 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>自治会積立金</t>
-    <rPh sb="0" eb="6">
-      <t>ジチカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>前期合計</t>
-    <rPh sb="0" eb="1">
-      <t>ゼn</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>後期合計</t>
-    <rPh sb="0" eb="4">
-      <t>コウキゴウク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>総合計</t>
-    <rPh sb="0" eb="1">
-      <t xml:space="preserve">ソウ </t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>ネンドグ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>次年度繰越金</t>
-    <rPh sb="0" eb="6">
-      <t>ジネンド</t>
+    <rPh sb="0" eb="2">
+      <t>ジネn</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">ド </t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>クリコセィ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1407,7 +1427,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1564,12 +1584,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1597,46 +1611,70 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1986,14 +2024,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1"/>
     <row r="3" spans="1:6" ht="18" customHeight="1"/>
@@ -2338,84 +2376,84 @@
       <c r="F44" s="2"/>
     </row>
     <row r="45" spans="1:6" ht="13" customHeight="1">
-      <c r="A45" s="66"/>
-      <c r="B45" s="66"/>
-      <c r="C45" s="66"/>
-      <c r="D45" s="66"/>
-      <c r="E45" s="66"/>
-      <c r="F45" s="66"/>
+      <c r="A45" s="61"/>
+      <c r="B45" s="61"/>
+      <c r="C45" s="61"/>
+      <c r="D45" s="61"/>
+      <c r="E45" s="61"/>
+      <c r="F45" s="61"/>
     </row>
     <row r="46" spans="1:6" ht="13" customHeight="1">
-      <c r="A46" s="67"/>
-      <c r="B46" s="67"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="67"/>
+      <c r="A46" s="62"/>
+      <c r="B46" s="62"/>
+      <c r="C46" s="62"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="62"/>
+      <c r="F46" s="62"/>
     </row>
     <row r="47" spans="1:6" ht="13" customHeight="1">
-      <c r="A47" s="67"/>
-      <c r="B47" s="67"/>
-      <c r="C47" s="67"/>
-      <c r="D47" s="67"/>
-      <c r="E47" s="67"/>
-      <c r="F47" s="67"/>
+      <c r="A47" s="62"/>
+      <c r="B47" s="62"/>
+      <c r="C47" s="62"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="62"/>
+      <c r="F47" s="62"/>
     </row>
     <row r="48" spans="1:6" ht="13" customHeight="1">
-      <c r="A48" s="67"/>
-      <c r="B48" s="67"/>
-      <c r="C48" s="67"/>
-      <c r="D48" s="67"/>
-      <c r="E48" s="67"/>
-      <c r="F48" s="67"/>
+      <c r="A48" s="62"/>
+      <c r="B48" s="62"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
     </row>
     <row r="49" spans="1:6" ht="13" customHeight="1">
-      <c r="A49" s="67"/>
-      <c r="B49" s="67"/>
-      <c r="C49" s="67"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="67"/>
-      <c r="F49" s="67"/>
+      <c r="A49" s="62"/>
+      <c r="B49" s="62"/>
+      <c r="C49" s="62"/>
+      <c r="D49" s="62"/>
+      <c r="E49" s="62"/>
+      <c r="F49" s="62"/>
     </row>
     <row r="50" spans="1:6" ht="13" customHeight="1">
-      <c r="A50" s="67"/>
-      <c r="B50" s="67"/>
-      <c r="C50" s="67"/>
-      <c r="D50" s="67"/>
-      <c r="E50" s="67"/>
-      <c r="F50" s="67"/>
+      <c r="A50" s="62"/>
+      <c r="B50" s="62"/>
+      <c r="C50" s="62"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="62"/>
+      <c r="F50" s="62"/>
     </row>
     <row r="51" spans="1:6" ht="13" customHeight="1">
-      <c r="A51" s="67"/>
-      <c r="B51" s="67"/>
-      <c r="C51" s="67"/>
-      <c r="D51" s="67"/>
-      <c r="E51" s="67"/>
-      <c r="F51" s="67"/>
+      <c r="A51" s="62"/>
+      <c r="B51" s="62"/>
+      <c r="C51" s="62"/>
+      <c r="D51" s="62"/>
+      <c r="E51" s="62"/>
+      <c r="F51" s="62"/>
     </row>
     <row r="52" spans="1:6" ht="13" customHeight="1">
-      <c r="A52" s="67"/>
-      <c r="B52" s="67"/>
-      <c r="C52" s="67"/>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="67"/>
+      <c r="A52" s="62"/>
+      <c r="B52" s="62"/>
+      <c r="C52" s="62"/>
+      <c r="D52" s="62"/>
+      <c r="E52" s="62"/>
+      <c r="F52" s="62"/>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="68" t="s">
         <v>90</v>
       </c>
       <c r="B53" s="68"/>
-      <c r="C53" s="67">
+      <c r="C53" s="62">
         <f>SUM(C5:C52)</f>
         <v>0</v>
       </c>
-      <c r="D53" s="67">
+      <c r="D53" s="62">
         <f>SUM(D5:D52)</f>
         <v>0</v>
       </c>
-      <c r="E53" s="67"/>
-      <c r="F53" s="67"/>
+      <c r="E53" s="62"/>
+      <c r="F53" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2453,14 +2491,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1"/>
     <row r="3" spans="1:6" ht="18" customHeight="1"/>
@@ -2829,74 +2867,84 @@
       <c r="F47" s="2"/>
     </row>
     <row r="48" spans="1:6" ht="20" customHeight="1">
-      <c r="A48" s="70" t="s">
+      <c r="A48" s="69" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" s="70"/>
+      <c r="C48" s="62">
+        <f>SUMIF('収支（前期）'!F:F,"前年度繰越金",'収支（前期）'!C:C)+SUMIF('収支（後期）'!F5:F47,"前年度繰越金",'収支（後期）'!C5:C47)</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
+    </row>
+    <row r="49" spans="1:6" ht="20" customHeight="1">
+      <c r="A49" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="B48" s="71"/>
-      <c r="C48" s="67"/>
-      <c r="D48" s="67"/>
-      <c r="E48" s="67"/>
-      <c r="F48" s="67"/>
-    </row>
-    <row r="49" spans="1:6" ht="20" customHeight="1">
-      <c r="A49" s="70" t="s">
+      <c r="B49" s="70"/>
+      <c r="C49" s="62">
+        <f>SUMIF('収支（前期）'!F:F,"自治会積立金",'収支（前期）'!C:C)+SUMIF('収支（後期）'!F5:F47,"自治会積立金",'収支（後期）'!C5:C47)</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="62"/>
+      <c r="E49" s="62"/>
+      <c r="F49" s="62"/>
+    </row>
+    <row r="50" spans="1:6" ht="20" customHeight="1">
+      <c r="A50" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="B49" s="71"/>
-      <c r="C49" s="67"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="67"/>
-      <c r="F49" s="67"/>
-    </row>
-    <row r="50" spans="1:6" ht="20" customHeight="1">
-      <c r="A50" s="70" t="s">
+      <c r="B50" s="70"/>
+      <c r="C50" s="62"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="62"/>
+      <c r="F50" s="62"/>
+    </row>
+    <row r="51" spans="1:6" ht="20" customHeight="1">
+      <c r="A51" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="B50" s="71"/>
-      <c r="C50" s="67"/>
-      <c r="D50" s="67"/>
-      <c r="E50" s="67"/>
-      <c r="F50" s="67"/>
-    </row>
-    <row r="51" spans="1:6" ht="20" customHeight="1">
-      <c r="A51" s="70" t="s">
+      <c r="B51" s="70"/>
+      <c r="C51" s="62">
+        <f>SUM(C5:C47)</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="62">
+        <f>SUM(D5:D47)</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="62"/>
+      <c r="F51" s="62"/>
+    </row>
+    <row r="52" spans="1:6" ht="20" customHeight="1">
+      <c r="A52" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="B51" s="71"/>
-      <c r="C51" s="67">
-        <f>SUM(C5:C47)</f>
-        <v>0</v>
-      </c>
-      <c r="D51" s="67">
-        <f>SUM(D5:D47)</f>
-        <v>0</v>
-      </c>
-      <c r="E51" s="67"/>
-      <c r="F51" s="67"/>
-    </row>
-    <row r="52" spans="1:6" ht="20" customHeight="1">
-      <c r="A52" s="70" t="s">
-        <v>95</v>
-      </c>
-      <c r="B52" s="71"/>
-      <c r="C52" s="67">
+      <c r="B52" s="70"/>
+      <c r="C52" s="62">
         <f>SUM(C50:C51)</f>
         <v>0</v>
       </c>
-      <c r="D52" s="67">
+      <c r="D52" s="62">
         <f>SUM(D50:D51)</f>
         <v>0</v>
       </c>
-      <c r="E52" s="69"/>
-      <c r="F52" s="69"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="70"/>
-      <c r="B53" s="71"/>
-      <c r="C53" s="72"/>
-      <c r="D53" s="67"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="67"/>
+      <c r="A53" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="B53" s="70"/>
+      <c r="C53" s="62"/>
+      <c r="D53" s="62"/>
+      <c r="E53" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="F53" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2936,14 +2984,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
@@ -3263,25 +3311,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="27">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
     </row>
     <row r="3" spans="1:8" ht="14" customHeight="1"/>
     <row r="4" spans="1:8" ht="24">
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="53" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="78">
+        <f>'収支（後期）'!C52</f>
+        <v>0</v>
+      </c>
       <c r="E4" s="9" t="s">
         <v>54</v>
       </c>
@@ -3289,13 +3340,16 @@
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:8" ht="24">
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="53" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="10"/>
+      <c r="D5" s="78">
+        <f>'収支（後期）'!D52</f>
+        <v>0</v>
+      </c>
       <c r="E5" s="9" t="s">
         <v>53</v>
       </c>
@@ -3304,20 +3358,21 @@
     </row>
     <row r="6" spans="1:8" ht="14" customHeight="1">
       <c r="B6" s="11"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="11"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="79"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="B7" s="55"/>
+      <c r="B7" s="53"/>
       <c r="C7" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="76">
-        <v>42342</v>
-      </c>
-      <c r="E7" s="75"/>
+      <c r="D7" s="80">
+        <f>'収支（後期）'!C48</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="12"/>
       <c r="F7" s="13"/>
     </row>
     <row r="8" spans="1:8" ht="21" thickBot="1">
@@ -3326,8 +3381,8 @@
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="54" t="s">
+      <c r="E8" s="65"/>
+      <c r="F8" s="52" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3344,7 +3399,7 @@
       <c r="E9" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="61" t="s">
+      <c r="F9" s="59" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3353,9 +3408,12 @@
         <v>35</v>
       </c>
       <c r="C10" s="19"/>
-      <c r="D10" s="20"/>
+      <c r="D10" s="77">
+        <f>D7</f>
+        <v>0</v>
+      </c>
       <c r="E10" s="40">
-        <f t="shared" ref="E10:E17" si="0">C10-D10</f>
+        <f>D10-C10</f>
         <v>0</v>
       </c>
       <c r="F10" s="46" t="s">
@@ -3369,7 +3427,7 @@
       <c r="C11" s="23"/>
       <c r="D11" s="24"/>
       <c r="E11" s="41">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E11:E17" si="0">C11-D11</f>
         <v>0</v>
       </c>
       <c r="F11" s="8" t="s">
@@ -3447,11 +3505,14 @@
       </c>
     </row>
     <row r="17" spans="2:6" ht="21" thickBot="1">
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="54" t="s">
         <v>83</v>
       </c>
       <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
+      <c r="D17" s="28">
+        <f>'収支（後期）'!C49</f>
+        <v>0</v>
+      </c>
       <c r="E17" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3461,14 +3522,14 @@
       </c>
     </row>
     <row r="18" spans="2:6" ht="21" thickBot="1">
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="76">
         <f>SUM(C10:C17)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="76">
         <f>SUM(D10:D17)</f>
         <v>0</v>
       </c>
@@ -3500,7 +3561,7 @@
       <c r="E20" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="61" t="s">
+      <c r="F20" s="59" t="s">
         <v>89</v>
       </c>
     </row>
@@ -3617,14 +3678,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" ht="21" thickBot="1">
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="76">
         <f>SUM(C21:C28)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="76">
         <f>SUM(D21:D28)</f>
         <v>0</v>
       </c>
@@ -3642,13 +3703,13 @@
       <c r="F30" s="11"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="52">
+      <c r="D31" s="73">
         <f>D18</f>
         <v>0</v>
       </c>
@@ -3658,13 +3719,13 @@
       <c r="F31" s="11"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="55" t="s">
+      <c r="B32" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="52">
+      <c r="D32" s="73">
         <f>D29</f>
         <v>0</v>
       </c>
@@ -3677,10 +3738,10 @@
       <c r="B33" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D33" s="53">
+      <c r="C33" s="74" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" s="75">
         <f>D31-D32</f>
         <v>0</v>
       </c>
@@ -3740,19 +3801,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="27">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
     </row>
     <row r="3" spans="1:8" ht="14" customHeight="1"/>
     <row r="4" spans="1:8" ht="24">
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="53" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="34" t="s">
@@ -3766,7 +3827,7 @@
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:8" ht="24">
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="53" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="34" t="s">
@@ -3793,7 +3854,7 @@
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
-      <c r="F7" s="54" t="s">
+      <c r="F7" s="52" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3810,7 +3871,7 @@
       <c r="E8" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="62" t="s">
+      <c r="F8" s="60" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3824,7 +3885,7 @@
         <f t="shared" ref="E9:E16" si="0">C9-D9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="57" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3838,7 +3899,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="60" t="s">
+      <c r="F10" s="58" t="s">
         <v>85</v>
       </c>
     </row>
@@ -3852,7 +3913,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F11" s="60" t="s">
+      <c r="F11" s="58" t="s">
         <v>63</v>
       </c>
     </row>
@@ -3866,7 +3927,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F12" s="60" t="s">
+      <c r="F12" s="58" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3880,7 +3941,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F13" s="60" t="s">
+      <c r="F13" s="58" t="s">
         <v>67</v>
       </c>
     </row>
@@ -3894,7 +3955,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F14" s="60" t="s">
+      <c r="F14" s="58" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3908,12 +3969,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" s="60" t="s">
+      <c r="F15" s="58" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="21" thickBot="1">
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="54" t="s">
         <v>83</v>
       </c>
       <c r="C16" s="27"/>
@@ -3927,7 +3988,7 @@
       </c>
     </row>
     <row r="17" spans="2:6" ht="21" thickBot="1">
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="56" t="s">
         <v>42</v>
       </c>
       <c r="C17" s="30">
@@ -3966,7 +4027,7 @@
       <c r="E19" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="62" t="s">
+      <c r="F19" s="60" t="s">
         <v>89</v>
       </c>
     </row>
@@ -4083,7 +4144,7 @@
       </c>
     </row>
     <row r="28" spans="2:6" ht="21" thickBot="1">
-      <c r="B28" s="58" t="s">
+      <c r="B28" s="56" t="s">
         <v>42</v>
       </c>
       <c r="C28" s="30">
@@ -4142,7 +4203,7 @@
     </row>
     <row r="37" spans="2:6">
       <c r="D37" s="3"/>
-      <c r="F37" s="57"/>
+      <c r="F37" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="1">
